--- a/models/6363_SOTP_Model.xlsx
+++ b/models/6363_SOTP_Model.xlsx
@@ -771,7 +771,7 @@
     <row r="18">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>DCF cross-check as of 2026-09-06 23:29 from 6363_DCF_Model_20260413.xlsx (static snapshot — regenerate after re-running the DCF)</t>
+          <t>DCF cross-check as of 2026-09-07 01:33 from 6363_DCF_Model_20260413.xlsx (static snapshot — regenerate after re-running the DCF)</t>
         </is>
       </c>
     </row>
